--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailProd001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailProd001.xlsx
@@ -415,7 +415,7 @@
   <numFmts count="1">
     <numFmt numFmtId="182" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,15 +460,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -476,7 +467,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,12 +477,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -527,12 +512,12 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -858,214 +843,214 @@
     <col min="18" max="18" width="13.08984375" style="1" customWidth="1"/>
     <col min="19" max="19" width="12.1796875" style="1" customWidth="1"/>
     <col min="20" max="20" width="12.6328125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="8.7265625" style="4"/>
-    <col min="23" max="23" width="11.6328125" style="4" customWidth="1"/>
-    <col min="24" max="25" width="13" style="4" customWidth="1"/>
-    <col min="26" max="26" width="12.81640625" style="4" customWidth="1"/>
-    <col min="27" max="28" width="20" style="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="13.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="4" customWidth="1"/>
-    <col min="33" max="33" width="16.54296875" style="4" customWidth="1"/>
-    <col min="34" max="35" width="8.7265625" style="4"/>
-    <col min="36" max="36" width="12" style="4" customWidth="1"/>
-    <col min="37" max="37" width="12.26953125" style="4" customWidth="1"/>
-    <col min="38" max="38" width="12" style="4" customWidth="1"/>
-    <col min="39" max="39" width="10.453125" style="4" customWidth="1"/>
-    <col min="40" max="64" width="8.7265625" style="4"/>
+    <col min="21" max="22" width="8.7265625" style="2"/>
+    <col min="23" max="23" width="11.6328125" style="2" customWidth="1"/>
+    <col min="24" max="25" width="13" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.81640625" style="2" customWidth="1"/>
+    <col min="27" max="28" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" style="2" customWidth="1"/>
+    <col min="33" max="33" width="16.54296875" style="2" customWidth="1"/>
+    <col min="34" max="35" width="8.7265625" style="2"/>
+    <col min="36" max="36" width="12" style="2" customWidth="1"/>
+    <col min="37" max="37" width="12.26953125" style="2" customWidth="1"/>
+    <col min="38" max="38" width="12" style="2" customWidth="1"/>
+    <col min="39" max="39" width="10.453125" style="2" customWidth="1"/>
+    <col min="40" max="64" width="8.7265625" style="2"/>
     <col min="65" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="5" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:64" s="3" customFormat="1">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AT1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AU1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AW1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AX1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AY1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="AZ1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BB1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BC1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BD1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BE1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BF1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BG1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BH1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BI1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BJ1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BK1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BL1" s="5" t="s">
         <v>26</v>
       </c>
     </row>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailProd001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcMonthReportDetailProd001.xlsx
@@ -27,7 +27,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -37,7 +36,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -53,7 +51,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -63,7 +60,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -79,7 +75,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -89,7 +84,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -105,7 +99,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -115,37 +108,10 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 1-6：到期未兑付：本字段为是，且有余额的情况</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>作者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-提前兑付、延期兑付、按期兑付</t>
         </r>
       </text>
     </comment>
@@ -154,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
   <si>
     <t>金额类型</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -232,10 +198,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>兑付类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>住户</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -406,6 +368,763 @@
   <si>
     <t>431000新疆</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#{keyList.dataTypeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.prodid}</t>
+  </si>
+  <si>
+    <t>#{keyList.prodName}</t>
+  </si>
+  <si>
+    <t>#{keyList.vdateStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.mdateStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.raiseTypeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.ivstorientationStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.ccyStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.manageTypeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.fiduciaryDutyStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.operateModeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.termdays}</t>
+  </si>
+  <si>
+    <t>#{keyList.termtypeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isConstracteStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.transferTypeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isMarketFundStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isThisTremStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isEndTremStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isEndSubsistStr}</t>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.ordIdentified01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Dv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.ordIdentified02Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.ordIdentified03Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.ordIdentified04Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.ordIdentified05Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.ordIdentified06Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.ordIdentifiedAll</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Dv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Dv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace02Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace03Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace04Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace05Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace06Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace07Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace08Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace09Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace10Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace11Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace12Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace13Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace14Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace15Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace16Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace17Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace18Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace19Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace20Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace21Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace22Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace23Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace24Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace25Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace26Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace27Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace28Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace29Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace30Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace31Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace32Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace33Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace34Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace35Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlace36Dv}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#{keyList.buyPlaceAll</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Dv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -415,25 +1134,22 @@
   <numFmts count="1">
     <numFmt numFmtId="182" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -441,28 +1157,30 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -507,17 +1225,18 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -823,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BL1"/>
+  <dimension ref="A1:BK2"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="9" style="1" customWidth="1"/>
@@ -842,25 +1561,24 @@
     <col min="17" max="17" width="12.90625" style="1" customWidth="1"/>
     <col min="18" max="18" width="13.08984375" style="1" customWidth="1"/>
     <col min="19" max="19" width="12.1796875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="12.6328125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="8.7265625" style="2"/>
-    <col min="23" max="23" width="11.6328125" style="2" customWidth="1"/>
-    <col min="24" max="25" width="13" style="2" customWidth="1"/>
-    <col min="26" max="26" width="12.81640625" style="2" customWidth="1"/>
-    <col min="27" max="28" width="20" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="2" customWidth="1"/>
-    <col min="33" max="33" width="16.54296875" style="2" customWidth="1"/>
-    <col min="34" max="35" width="8.7265625" style="2"/>
-    <col min="36" max="36" width="12" style="2" customWidth="1"/>
-    <col min="37" max="37" width="12.26953125" style="2" customWidth="1"/>
-    <col min="38" max="38" width="12" style="2" customWidth="1"/>
-    <col min="39" max="39" width="10.453125" style="2" customWidth="1"/>
-    <col min="40" max="64" width="8.7265625" style="2"/>
-    <col min="65" max="16384" width="8.7265625" style="1"/>
+    <col min="20" max="21" width="8.7265625" style="2"/>
+    <col min="22" max="22" width="11.6328125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="13" style="2" customWidth="1"/>
+    <col min="25" max="25" width="12.81640625" style="2" customWidth="1"/>
+    <col min="26" max="27" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13" style="2" customWidth="1"/>
+    <col min="32" max="32" width="16.54296875" style="2" customWidth="1"/>
+    <col min="33" max="34" width="8.7265625" style="2"/>
+    <col min="35" max="35" width="12" style="2" customWidth="1"/>
+    <col min="36" max="36" width="12.26953125" style="2" customWidth="1"/>
+    <col min="37" max="37" width="12" style="2" customWidth="1"/>
+    <col min="38" max="38" width="10.453125" style="2" customWidth="1"/>
+    <col min="39" max="63" width="8.7265625" style="2"/>
+    <col min="64" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" s="3" customFormat="1">
+    <row r="1" spans="1:63" s="3" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -918,7 +1636,7 @@
       <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="5" t="s">
@@ -943,7 +1661,7 @@
         <v>26</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="AC1" s="5" t="s">
         <v>36</v>
@@ -955,19 +1673,19 @@
         <v>38</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="AG1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="AH1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="AJ1" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="AK1" s="5" t="s">
         <v>41</v>
@@ -976,31 +1694,31 @@
         <v>42</v>
       </c>
       <c r="AM1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AN1" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="AN1" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="AO1" s="5" t="s">
         <v>44</v>
       </c>
       <c r="AP1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="AQ1" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="AR1" s="5" t="s">
         <v>46</v>
       </c>
       <c r="AS1" s="5" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="AT1" s="5" t="s">
         <v>33</v>
       </c>
       <c r="AU1" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AV1" s="5" t="s">
         <v>48</v>
@@ -1009,10 +1727,10 @@
         <v>49</v>
       </c>
       <c r="AX1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY1" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="AY1" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="AZ1" s="5" t="s">
         <v>51</v>
@@ -1048,10 +1766,198 @@
         <v>61</v>
       </c>
       <c r="BK1" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:63">
+      <c r="A2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="5" t="s">
-        <v>26</v>
+      <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AL2" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM2" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO2" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP2" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ2" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AR2" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS2" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AT2" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU2" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV2" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AW2" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX2" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY2" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ2" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="BB2" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="BC2" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="BD2" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="BE2" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF2" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="BG2" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="BH2" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="BI2" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BJ2" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK2" s="6" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
